--- a/parameter_lists/files/device_id.xlsx
+++ b/parameter_lists/files/device_id.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal (H.Tavakkoli)\python\sw_setting\parameter_lists\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Protocol_matchbox_h7\Fw\fw_matchbox_h7\src\library\parameter_lists\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676E72F1-3AF0-413D-A66D-0696DDE3D877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EC7090-30A2-4153-80DF-166C5FAB2A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeviceId" sheetId="10" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
   <si>
     <t>Decription</t>
   </si>
@@ -63,21 +63,66 @@
     <t>p_imu_master_v1</t>
   </si>
   <si>
+    <t>rasta</t>
+  </si>
+  <si>
     <t>datalogger_v3_main</t>
   </si>
   <si>
+    <t>dragon</t>
+  </si>
+  <si>
     <t>datalogger_v3_slave</t>
   </si>
   <si>
+    <t>ani_sc</t>
+  </si>
+  <si>
+    <t>ani_sc_m</t>
+  </si>
+  <si>
+    <t>matchbox</t>
+  </si>
+  <si>
+    <t>pardis</t>
+  </si>
+  <si>
+    <t>pstar_main</t>
+  </si>
+  <si>
+    <t>pstar_alg</t>
+  </si>
+  <si>
     <t>sc_mb_imu_master_v1p4</t>
   </si>
   <si>
+    <t>blue_dragon_main</t>
+  </si>
+  <si>
+    <t>blue_dragon_alg</t>
+  </si>
+  <si>
+    <t>atlas_main</t>
+  </si>
+  <si>
+    <t>atlas_alg</t>
+  </si>
+  <si>
     <t>mini_host</t>
   </si>
   <si>
     <t>host</t>
   </si>
   <si>
+    <t>mohajer</t>
+  </si>
+  <si>
+    <t>sayyad</t>
+  </si>
+  <si>
+    <t>ccpu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Name </t>
   </si>
   <si>
@@ -138,10 +183,10 @@
     <t>eVirtualParameterId_BlueDragonNormalFrame</t>
   </si>
   <si>
-    <t>test1</t>
-  </si>
-  <si>
-    <t>test2</t>
+    <t>MatchboxFrame1</t>
+  </si>
+  <si>
+    <t>eVirtualParameterId_MatchboxFrame1</t>
   </si>
 </sst>
 </file>
@@ -212,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -234,7 +279,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,7 +593,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1">
         <v>2</v>
@@ -561,7 +605,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>3</v>
@@ -585,7 +629,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1">
         <v>5</v>
@@ -597,7 +641,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1">
         <v>6</v>
@@ -609,7 +653,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1">
         <v>7</v>
@@ -621,7 +665,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1">
         <v>1000</v>
@@ -635,7 +679,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1">
         <v>1001</v>
@@ -643,82 +687,160 @@
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="A11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
+      <c r="A12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
+      <c r="A13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1005</v>
+      </c>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
+      <c r="A15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1007</v>
+      </c>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="A16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1008</v>
+      </c>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="A17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1009</v>
+      </c>
+      <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
+      <c r="A18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1010</v>
+      </c>
+      <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
+      <c r="A19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1011</v>
+      </c>
+      <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+      <c r="A20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1012</v>
+      </c>
+      <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
+      <c r="A21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1013</v>
+      </c>
+      <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
+      <c r="A22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1014</v>
+      </c>
+      <c r="D22" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -727,7 +849,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92C7991-422B-4293-A5E3-612B865DECEF}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.140625" customWidth="1"/>
@@ -740,27 +862,27 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B2" s="6">
         <v>64000</v>
@@ -768,7 +890,7 @@
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="5" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F2" s="6">
         <v>29</v>
@@ -776,7 +898,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B3" s="6">
         <v>64001</v>
@@ -784,7 +906,7 @@
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F3" s="6">
         <v>56</v>
@@ -792,7 +914,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B4" s="6">
         <v>64002</v>
@@ -800,7 +922,7 @@
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="5" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F4" s="6">
         <v>28</v>
@@ -808,7 +930,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B5" s="6">
         <v>64003</v>
@@ -816,7 +938,7 @@
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="5" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F5" s="6">
         <v>56</v>
@@ -824,7 +946,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B6" s="6">
         <v>64004</v>
@@ -832,7 +954,7 @@
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="5" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F6" s="6">
         <v>30</v>
@@ -840,7 +962,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B7" s="6">
         <v>64005</v>
@@ -848,7 +970,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="5" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F7" s="6">
         <v>34</v>
@@ -856,7 +978,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B8" s="6">
         <v>64006</v>
@@ -864,10 +986,26 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="5" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F8" s="6">
         <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="6">
+        <v>64007</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="6">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
